--- a/public/kk-eulnaeyeokseo.xlsx
+++ b/public/kk-eulnaeyeokseo.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10802"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F88FF39-E20A-9447-B67F-1D38115AFDF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4016AB8-AF5B-9147-B3EB-37ADBDCA13F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8760" yWindow="860" windowWidth="38400" windowHeight="19060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="양식" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -497,36 +497,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF6E7480"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF16181C"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF6E7480"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF6E7480"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF16181C"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF6E7480"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF6E7480"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF6E7480"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF16181C"/>
       </bottom>
       <diagonal/>
     </border>
@@ -621,20 +591,77 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF6E7480"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF6E7480"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF6E7480"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF16181C"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF6E7480"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF16181C"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF6E7480"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF16181C"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF6E7480"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF6E7480"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF16181C"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF6E7480"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF6E7480"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF16181C"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -642,6 +669,48 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -657,62 +726,29 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1061,356 +1097,361 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="24" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="9" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
+      <c r="P1" s="21"/>
+      <c r="Q1" s="21"/>
+      <c r="R1" s="21"/>
+      <c r="S1" s="21"/>
+      <c r="T1" s="21"/>
+      <c r="U1" s="21"/>
       <c r="Z1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:26" ht="24" customHeight="1">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="21"/>
+      <c r="P2" s="21"/>
+      <c r="Q2" s="21"/>
+      <c r="R2" s="21"/>
+      <c r="S2" s="21"/>
+      <c r="T2" s="21"/>
+      <c r="U2" s="21"/>
     </row>
     <row r="3" spans="1:26" ht="24" customHeight="1">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11" t="s">
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="11"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="11"/>
-      <c r="T3" s="11"/>
-      <c r="U3" s="11"/>
-      <c r="V3" s="11"/>
-      <c r="W3" s="11"/>
-      <c r="X3" s="11"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
+      <c r="T3" s="23"/>
+      <c r="U3" s="23"/>
+      <c r="V3" s="23"/>
+      <c r="W3" s="23"/>
+      <c r="X3" s="23"/>
     </row>
     <row r="5" spans="1:26" ht="24" customHeight="1">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="12"/>
-      <c r="U5" s="12"/>
-      <c r="V5" s="12"/>
-      <c r="W5" s="12"/>
-      <c r="X5" s="12"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="24"/>
+      <c r="Q5" s="24"/>
+      <c r="R5" s="24"/>
+      <c r="S5" s="24"/>
+      <c r="T5" s="24"/>
+      <c r="U5" s="24"/>
+      <c r="V5" s="24"/>
+      <c r="W5" s="24"/>
+      <c r="X5" s="24"/>
       <c r="Z5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="24" customHeight="1">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="24" t="s">
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="L6" s="24" t="s">
+      <c r="L6" s="11"/>
+      <c r="M6" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="M6" s="13" t="s">
+      <c r="N6" s="11"/>
+      <c r="O6" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13" t="s">
+      <c r="P6" s="10"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="R6" s="13"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
-      <c r="U6" s="14" t="s">
+      <c r="S6" s="10"/>
+      <c r="T6" s="11"/>
+      <c r="U6" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="V6" s="14"/>
-      <c r="W6" s="14"/>
-      <c r="X6" s="14"/>
+      <c r="V6" s="18"/>
+      <c r="W6" s="18"/>
+      <c r="X6" s="18"/>
       <c r="Z6" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="24" customHeight="1">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="3" t="s">
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="L7" s="28"/>
+      <c r="M7" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="M7" s="15" t="s">
+      <c r="N7" s="28"/>
+      <c r="O7" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="N7" s="15"/>
-      <c r="O7" s="15"/>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="15" t="s">
+      <c r="P7" s="27"/>
+      <c r="Q7" s="28"/>
+      <c r="R7" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="R7" s="15"/>
-      <c r="S7" s="15"/>
-      <c r="T7" s="15"/>
-      <c r="U7" s="16" t="s">
+      <c r="S7" s="27"/>
+      <c r="T7" s="28"/>
+      <c r="U7" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="V7" s="16"/>
-      <c r="W7" s="16"/>
-      <c r="X7" s="16"/>
+      <c r="V7" s="19"/>
+      <c r="W7" s="19"/>
+      <c r="X7" s="19"/>
       <c r="Z7" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="24" customHeight="1">
-      <c r="A8" s="17" t="s">
+    <row r="8" spans="1:26" ht="24" customHeight="1" thickBot="1">
+      <c r="A8" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="17"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="18" t="s">
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="30"/>
+      <c r="P8" s="30"/>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="R8" s="18"/>
-      <c r="S8" s="18"/>
-      <c r="T8" s="18"/>
-      <c r="U8" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="V8" s="19"/>
-      <c r="W8" s="19"/>
-      <c r="X8" s="19"/>
+      <c r="S8" s="30"/>
+      <c r="T8" s="31"/>
+      <c r="U8" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="V8" s="15"/>
+      <c r="W8" s="15"/>
+      <c r="X8" s="15"/>
       <c r="Z8" s="2" t="s">
         <v>23</v>
       </c>
     </row>
+    <row r="9" spans="1:26" ht="24" customHeight="1" thickBot="1"/>
     <row r="10" spans="1:26" ht="24" customHeight="1">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="20"/>
-      <c r="N10" s="20"/>
-      <c r="O10" s="20"/>
-      <c r="P10" s="20"/>
-      <c r="Q10" s="21" t="s">
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="R10" s="21"/>
-      <c r="S10" s="21"/>
-      <c r="T10" s="21"/>
-      <c r="U10" s="21"/>
-      <c r="V10" s="21"/>
-      <c r="W10" s="21"/>
-      <c r="X10" s="21"/>
+      <c r="R10" s="17"/>
+      <c r="S10" s="17"/>
+      <c r="T10" s="17"/>
+      <c r="U10" s="17"/>
+      <c r="V10" s="17"/>
+      <c r="W10" s="17"/>
+      <c r="X10" s="17"/>
       <c r="Z10" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="24" customHeight="1">
-      <c r="A11" s="20"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
-      <c r="K11" s="20"/>
-      <c r="L11" s="20"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="20"/>
-      <c r="O11" s="20"/>
-      <c r="P11" s="20"/>
-      <c r="Q11" s="21"/>
-      <c r="R11" s="21"/>
-      <c r="S11" s="21"/>
-      <c r="T11" s="21"/>
-      <c r="U11" s="21"/>
-      <c r="V11" s="21"/>
-      <c r="W11" s="21"/>
-      <c r="X11" s="21"/>
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="17"/>
+      <c r="U11" s="17"/>
+      <c r="V11" s="17"/>
+      <c r="W11" s="17"/>
+      <c r="X11" s="17"/>
       <c r="Z11" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="20" spans="25:25" ht="24" customHeight="1">
-      <c r="Y20" s="25"/>
+      <c r="Y20" s="6"/>
     </row>
     <row r="42" spans="1:26" ht="24" customHeight="1">
-      <c r="A42" s="22" t="s">
+      <c r="A42" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B42" s="22"/>
-      <c r="C42" s="22"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="22"/>
-      <c r="F42" s="22"/>
-      <c r="G42" s="22"/>
-      <c r="H42" s="22"/>
-      <c r="I42" s="22"/>
-      <c r="J42" s="22"/>
-      <c r="K42" s="22"/>
-      <c r="L42" s="22"/>
-      <c r="M42" s="22"/>
-      <c r="N42" s="22"/>
-      <c r="O42" s="22"/>
-      <c r="P42" s="22"/>
-      <c r="Q42" s="22"/>
-      <c r="R42" s="22"/>
-      <c r="S42" s="23" t="s">
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="7"/>
+      <c r="K42" s="7"/>
+      <c r="L42" s="7"/>
+      <c r="M42" s="7"/>
+      <c r="N42" s="7"/>
+      <c r="O42" s="7"/>
+      <c r="P42" s="7"/>
+      <c r="Q42" s="7"/>
+      <c r="R42" s="7"/>
+      <c r="S42" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="T42" s="23"/>
-      <c r="U42" s="23"/>
-      <c r="V42" s="23"/>
-      <c r="W42" s="23"/>
-      <c r="X42" s="23"/>
+      <c r="T42" s="8"/>
+      <c r="U42" s="8"/>
+      <c r="V42" s="8"/>
+      <c r="W42" s="8"/>
+      <c r="X42" s="8"/>
       <c r="Z42" s="2" t="s">
         <v>28</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="A42:R42"/>
-    <mergeCell ref="S42:X42"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:P8"/>
-    <mergeCell ref="Q8:T8"/>
-    <mergeCell ref="U8:X8"/>
-    <mergeCell ref="A10:P11"/>
-    <mergeCell ref="Q10:X11"/>
-    <mergeCell ref="U6:X6"/>
-    <mergeCell ref="M7:P7"/>
-    <mergeCell ref="Q7:T7"/>
-    <mergeCell ref="U7:X7"/>
-    <mergeCell ref="M6:P6"/>
-    <mergeCell ref="Q6:T6"/>
+  <mergeCells count="24">
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="A8:Q8"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="R6:T6"/>
+    <mergeCell ref="O7:Q7"/>
+    <mergeCell ref="R7:T7"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M7:N7"/>
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="D1:U2"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="D3:X3"/>
     <mergeCell ref="A5:X5"/>
+    <mergeCell ref="A42:R42"/>
+    <mergeCell ref="S42:X42"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="U8:X8"/>
+    <mergeCell ref="A10:P11"/>
+    <mergeCell ref="Q10:X11"/>
+    <mergeCell ref="U6:X6"/>
+    <mergeCell ref="U7:X7"/>
+    <mergeCell ref="O6:Q6"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <dataValidations count="1">
@@ -1426,7 +1467,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1436,20 +1477,20 @@
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="5" customFormat="1" ht="15">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:5" s="3" customFormat="1" ht="15">
+      <c r="A1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="3" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1458,7 +1499,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="20">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -1475,7 +1516,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="20">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>38</v>
       </c>
@@ -1492,7 +1533,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="20">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -1509,7 +1550,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="20">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -1526,7 +1567,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="20">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>45</v>
       </c>
@@ -1543,7 +1584,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="20">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>47</v>
       </c>
@@ -1560,7 +1601,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="20">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>48</v>
       </c>
@@ -1577,7 +1618,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="20">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -1594,7 +1635,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="20">
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -1611,7 +1652,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="20">
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>52</v>
       </c>
@@ -1633,7 +1674,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="20">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>54</v>
       </c>
@@ -1650,7 +1691,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="20">
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>55</v>
       </c>
@@ -1667,7 +1708,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="20">
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>58</v>
       </c>
@@ -1684,7 +1725,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="20">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -1701,7 +1742,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="20">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -1718,7 +1759,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="20">
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>10</v>
       </c>
@@ -1735,7 +1776,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="20">
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -1752,7 +1793,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="20">
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -1769,33 +1810,6 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="20"/>
-    <row r="23" spans="1:5" ht="20"/>
-    <row r="24" spans="1:5" ht="20"/>
-    <row r="25" spans="1:5" ht="20"/>
-    <row r="26" spans="1:5" ht="20"/>
-    <row r="27" spans="1:5" ht="20"/>
-    <row r="28" spans="1:5" ht="20"/>
-    <row r="29" spans="1:5" ht="20"/>
-    <row r="30" spans="1:5" ht="20"/>
-    <row r="31" spans="1:5" ht="20"/>
-    <row r="32" spans="1:5" ht="20"/>
-    <row r="33" ht="20"/>
-    <row r="34" ht="20"/>
-    <row r="35" ht="20"/>
-    <row r="36" ht="20"/>
-    <row r="37" ht="20"/>
-    <row r="38" ht="20"/>
-    <row r="39" ht="20"/>
-    <row r="40" ht="20"/>
-    <row r="41" ht="20"/>
-    <row r="42" ht="20"/>
-    <row r="43" ht="20"/>
-    <row r="44" ht="20"/>
-    <row r="45" ht="20"/>
-    <row r="46" ht="20"/>
-    <row r="47" ht="20"/>
-    <row r="48" ht="20"/>
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <dataValidations count="2">
@@ -1820,307 +1834,307 @@
     <col min="2" max="2" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="6" customFormat="1" ht="34.75" customHeight="1">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:2" s="4" customFormat="1" ht="34.75" customHeight="1">
+      <c r="A1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A2" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="7" t="s">
+      <c r="B1" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="7" t="s">
+    <row r="3" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" s="6" customFormat="1" ht="34.75" customHeight="1">
-      <c r="A5" s="6" t="s">
+    <row r="4" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="4" customFormat="1" ht="34.75" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A6" s="7" t="s">
+      <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A6" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A7" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="8" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A8" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" s="6" customFormat="1" ht="34.75" customHeight="1">
-      <c r="A10" s="6" t="s">
+    <row r="9" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" s="4" customFormat="1" ht="34.75" customHeight="1">
+      <c r="A10" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A11" s="7" t="s">
+      <c r="B10" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A11" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="5" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A12" s="7" t="s">
+    <row r="12" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A12" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A13" s="7" t="s">
+    <row r="13" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A13" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="5" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A14" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="15" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A15" s="7" t="s">
+    <row r="15" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A15" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="5" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A16" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A17" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" s="6" customFormat="1" ht="34.75" customHeight="1">
-      <c r="A18" s="6" t="s">
+    <row r="17" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A17" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" s="4" customFormat="1" ht="34.75" customHeight="1">
+      <c r="A18" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A19" s="7" t="s">
+      <c r="B18" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A19" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A20" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A21" s="7" t="s">
+    <row r="21" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A21" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="22" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A22" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="7" t="s">
+    <row r="22" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A22" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A23" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="7" t="s">
+    <row r="23" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A23" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="24" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A24" s="7" t="s">
+    <row r="24" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A24" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="25" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A25" s="7" t="s">
+    <row r="25" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A25" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="5" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="26" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A26" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" s="6" customFormat="1" ht="34.75" customHeight="1">
-      <c r="A27" s="6" t="s">
+    <row r="26" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A26" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" s="4" customFormat="1" ht="34.75" customHeight="1">
+      <c r="A27" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A28" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" s="7" t="s">
+      <c r="B27" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A28" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A29" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B29" s="7" t="s">
+    <row r="29" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A29" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="30" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A30" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B30" s="7" t="s">
+    <row r="30" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A30" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="31" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A31" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B31" s="7" t="s">
+    <row r="31" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A31" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="32" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A32" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" s="6" customFormat="1" ht="34.75" customHeight="1">
-      <c r="A33" s="6" t="s">
+    <row r="32" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A32" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" s="4" customFormat="1" ht="34.75" customHeight="1">
+      <c r="A33" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A34" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B34" s="7" t="s">
+      <c r="B33" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A34" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="35" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A35" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B35" s="7" t="s">
+    <row r="35" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A35" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="36" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A36" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B36" s="7" t="s">
+    <row r="36" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A36" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="37" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A37" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A38" s="7" t="s">
+    <row r="37" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A37" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" s="5" customFormat="1" ht="24" customHeight="1">
+      <c r="A38" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="5" t="s">
         <v>100</v>
       </c>
     </row>
